--- a/output/yearend_review_report.xlsx
+++ b/output/yearend_review_report.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Source Analysis" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Distribution" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Bell Curve Chart" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Bell Curve Histogram" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -306,6 +307,156 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Composite Score Histogram</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Bell Curve Histogram'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Bell Curve Histogram'!$A$2:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Bell Curve Histogram'!$B$2:$B$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Bell Curve Histogram'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Bell Curve Histogram'!$A$2:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Bell Curve Histogram'!$B$2:$B$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <smooth val="1"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Score Bin</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Count</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -313,6 +464,33 @@
       <col>0</col>
       <colOff>0</colOff>
       <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="4320000"/>
@@ -3417,4 +3595,105 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Score Bin</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2.00–2.40</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2.40–2.80</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2.80–3.20</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3.20–3.60</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3.60–4.00</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4.00–4.40</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4.40–4.80</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/output/yearend_review_report.xlsx
+++ b/output/yearend_review_report.xlsx
@@ -49,12 +49,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -208,12 +208,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Bell Curve Chart'!$A$2:$A$4</f>
+              <f>'Bell Curve Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Bell Curve Chart'!$B$2:$B$4</f>
+              <f>'Bell Curve Chart'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -232,12 +232,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Bell Curve Chart'!$A$2:$A$4</f>
+              <f>'Bell Curve Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Bell Curve Chart'!$C$2:$C$4</f>
+              <f>'Bell Curve Chart'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -900,11 +900,11 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Exceeds Expectations</t>
+          <t>Meets Expectations</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -940,250 +940,250 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Exceeds Expectations</t>
+          <t>Meets Expectations</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>E003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>QA Lead</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>E003</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Priya Nair</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>QA Lead</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Meets Expectations</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>E006</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Vikram Reddy</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Developer</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E5" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Meets Expectations</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Rahul Mehta</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Meets Expectations</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>E011</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Ananya Rao</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Team Lead</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="E7" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Meets Expectations</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>E012</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Rohit Sharma</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Junior Developer</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>2.6</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Meets Expectations</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="n">
+      <c r="F8" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Needs Development</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>E006</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Vikram Reddy</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Senior Developer</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="3" t="n">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>E010</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Manoj Kumar</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Meets Expectations</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Rahul Mehta</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Meets Expectations</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>E011</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Ananya Rao</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Team Lead</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Meets Expectations</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>E012</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Rohit Sharma</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Junior Developer</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Meets Expectations</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>E010</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Manoj Kumar</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="2" t="n">
         <v>3.62</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="2" t="n">
         <v>41.7</v>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Meets Expectations</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="n">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Needs Development</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1220,11 +1220,11 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Meets Expectations</t>
+          <t>Unsatisfactory Performance</t>
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1260,11 +1260,11 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Meets Expectations</t>
+          <t>Unsatisfactory Performance</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1300,11 +1300,11 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Below Expectations</t>
+          <t>Severe Compliance/Performance Issue</t>
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1340,11 +1340,11 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Below Expectations</t>
+          <t>Severe Compliance/Performance Issue</t>
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3422,7 +3422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3466,16 +3466,16 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="n">
-        <v>20</v>
-      </c>
       <c r="D2" s="5" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3485,34 +3485,72 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Below Expectations</t>
+          <t>Needs Development</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>16.7</v>
       </c>
       <c r="E4" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Unsatisfactory Performance</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Severe Compliance/Performance Issue</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3527,7 +3565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3559,10 +3597,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3572,22 +3610,48 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Below Expectations</t>
+          <t>Needs Development</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Unsatisfactory Performance</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Severe Compliance/Performance Issue</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" t="n">
         <v>16.7</v>
       </c>
     </row>
